--- a/test_results/test_old_5budgets_8envs.xlsx
+++ b/test_results/test_old_5budgets_8envs.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 v2_16 v2_17 v2_18 v2_19 v2_20 v2_21 v2_22 v2_23 v2_24 v2_25 v2_26 v2_27 v2_28 v2_29 v2_30 v2_31) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5) (* v1_8 5) (* v1_9 5) (* v1_10 5) (* v1_11 5) (* v1_12 5) (* v1_13 5) (* v1_14 5) (* v1_15 5) (* v1_16 5) (* v1_17 5) (* v1_18 5) (* v1_19 5) (* v1_20 5) (* v1_21 5) (* v1_22 5) (* v1_23 5) (* v1_24 5) (* v1_25 5) (* v1_26 5) (* v1_27 5) (* v1_28 5) (* v1_29 5) (* v1_30 5) (* v1_31 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 v2_16 v2_17 v2_18 v2_19 v2_20 v2_21 v2_22 v2_23 v2_24 v2_25 v2_26 v2_27 v2_28 v2_29 v2_30 v2_31) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7 v1_8 v1_9 v1_10 v1_11 v1_12 v1_13 v1_14 v1_15 v1_16 v1_17 v1_18 v1_19 v1_20 v1_21 v1_22 v1_23 v1_24 v1_25 v1_26 v1_27 v1_28 v1_29 v1_30 v1_31) (Vec 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>24006</v>
       </c>
       <c r="F5" t="n">
-        <v>8008</v>
+        <v>108</v>
       </c>
       <c r="G5" t="n">
-        <v>66.64</v>
+        <v>99.55</v>
       </c>
       <c r="H5" t="n">
         <v>39.37</v>
@@ -656,7 +656,7 @@
         <v>260.63</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -673,32 +673,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>4759</v>
       </c>
       <c r="F6" t="n">
-        <v>977</v>
+        <v>576</v>
       </c>
       <c r="G6" t="n">
-        <v>79.47</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>78.75</v>
+        <v>77.55</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>221.25</v>
+        <v>222.45</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -715,32 +715,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>9760</v>
       </c>
       <c r="F7" t="n">
-        <v>1492</v>
+        <v>1091</v>
       </c>
       <c r="G7" t="n">
-        <v>84.70999999999999</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>79.94</v>
+        <v>78.75</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>220.06</v>
+        <v>221.25</v>
       </c>
       <c r="L7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -757,29 +757,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (Vec v2_1 v2_17 (* 2 (* v1_1 v2_1)) (* 2 (* v1_17 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (Vec v2_1 v2_17 (* 2 (* v1_1 v2_1)) (* 2 (* v1_17 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (Vec v2_2 v2_18 (* 2 (* v1_2 v2_2)) (* 2 (* v1_18 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (Vec v2_2 v2_18 (* 2 (* v1_2 v2_2)) (* 2 (* v1_18 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2))))) (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (Vec v2_1 v2_17 (* 2 (* v1_1 v2_1)) (* 2 (* v1_17 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (Vec v2_1 v2_17 (* 2 (* v1_1 v2_1)) (* 2 (* v1_17 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (Vec v2_2 v2_18 (* 2 (* v1_2 v2_2)) (* 2 (* v1_18 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (Vec v2_2 v2_18 (* 2 (* v1_2 v2_2)) (* 2 (* v1_18 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2))))) (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) (&lt;&lt; (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) (&lt;&lt; (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) 2))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) (&lt;&lt; (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) (&lt;&lt; (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) 2))))))) 1))</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>39762</v>
       </c>
       <c r="F8" t="n">
-        <v>8181</v>
+        <v>6577</v>
       </c>
       <c r="G8" t="n">
-        <v>79.43000000000001</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>78.75</v>
       </c>
       <c r="I8" t="n">
-        <v>85.93000000000001</v>
+        <v>81.14</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>214.07</v>
+        <v>218.86</v>
       </c>
       <c r="L8" t="n">
         <v>75</v>
@@ -883,32 +883,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_0 c2_2) (Vec c1_0 c1_2 c1_0 c1_2)) (&lt;&lt; (VecMinus (Vec c2_0 c2_2 c2_0 c2_2) (Vec c1_0 c1_2 c1_0 c1_2)) 2)) (VecMul (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) (&lt;&lt; (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_0 c2_2) (Vec c1_0 c1_2 c1_0 c1_2)) (&lt;&lt; (VecMinus (Vec c2_0 c2_2 c2_0 c2_2) (Vec c1_0 c1_2 c1_0 c1_2)) 2)) (VecMul (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) (&lt;&lt; (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) 2))) 1))</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>3757</v>
       </c>
       <c r="F11" t="n">
-        <v>3757</v>
+        <v>372</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>40.57</v>
       </c>
       <c r="I11" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>259.43</v>
+        <v>257.03</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -925,17 +925,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>7758</v>
       </c>
       <c r="F12" t="n">
-        <v>950</v>
+        <v>752</v>
       </c>
       <c r="G12" t="n">
-        <v>87.75</v>
+        <v>90.31</v>
       </c>
       <c r="H12" t="n">
         <v>41.77</v>
@@ -967,32 +967,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>31760</v>
       </c>
       <c r="F13" t="n">
-        <v>3619</v>
+        <v>3088</v>
       </c>
       <c r="G13" t="n">
-        <v>88.61</v>
+        <v>90.28</v>
       </c>
       <c r="H13" t="n">
         <v>44.16</v>
       </c>
       <c r="I13" t="n">
-        <v>51.35</v>
+        <v>47.76</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>248.65</v>
+        <v>252.24</v>
       </c>
       <c r="L13" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v2_0 v2_2) (&lt;&lt; (Vec v1_0 v1_2 v2_0 v2_2) 2)) (VecMul (Vec v1_1 v1_3 v2_1 v2_3) (&lt;&lt; (Vec v1_1 v1_3 v2_1 v2_3) 2))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v2_0 v2_2) (&lt;&lt; (Vec v1_0 v1_2 v2_0 v2_2) 2)) (VecMul (Vec v1_1 v1_3 v2_1 v2_3) (&lt;&lt; (Vec v1_1 v1_3 v2_1 v2_3) 2))) 1))</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>1756</v>
       </c>
       <c r="F14" t="n">
-        <v>1756</v>
+        <v>369</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>39.37</v>
       </c>
       <c r="I14" t="n">
-        <v>39.37</v>
+        <v>41.77</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>260.63</v>
+        <v>258.23</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1093,32 +1093,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2))) (VecAdd (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2)) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2))) (VecAdd (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2)) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2))))) (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecAdd (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2)) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2))) (VecAdd (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2)) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2))) (VecAdd (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2)) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2))))) (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecAdd (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2)) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>15759</v>
       </c>
       <c r="F16" t="n">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="G16" t="n">
-        <v>83.84999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H16" t="n">
         <v>42.97</v>
       </c>
       <c r="I16" t="n">
-        <v>48.96</v>
+        <v>45.36</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>251.04</v>
+        <v>254.64</v>
       </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
@@ -1135,32 +1135,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2))) (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0)) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (Vec 0 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 2 2 0)) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecMinus (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) (&lt;&lt; (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) 16)))) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>21507</v>
       </c>
       <c r="F17" t="n">
-        <v>4879</v>
+        <v>514</v>
       </c>
       <c r="G17" t="n">
-        <v>77.31</v>
+        <v>97.61</v>
       </c>
       <c r="H17" t="n">
         <v>40.57</v>
       </c>
       <c r="I17" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>258.23</v>
+        <v>257.03</v>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) (&lt;&lt; (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) 1))</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (Vec x9604 (+ (* x9613 x9615) x9617))) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (Vec x9604 (+ (* x9613 x9615) x9617))) 1))</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>1508</v>
       </c>
       <c r="F21" t="n">
-        <v>911</v>
+        <v>716</v>
       </c>
       <c r="G21" t="n">
-        <v>39.59</v>
+        <v>52.52</v>
       </c>
       <c r="H21" t="n">
         <v>73.95</v>
@@ -1328,7 +1328,7 @@
         <v>224.85</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3)) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>21006</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
         <v>99.93000000000001</v>
@@ -1445,16 +1445,16 @@
         <v>7.19</v>
       </c>
       <c r="I24" t="n">
-        <v>8.390000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>291.61</v>
+        <v>292.81</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1639,29 +1639,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) 2))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>19761</v>
       </c>
       <c r="F29" t="n">
-        <v>2522</v>
+        <v>2120</v>
       </c>
       <c r="G29" t="n">
-        <v>87.23999999999999</v>
+        <v>89.27</v>
       </c>
       <c r="H29" t="n">
         <v>77.55</v>
       </c>
       <c r="I29" t="n">
-        <v>82.34</v>
+        <v>79.94</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>217.66</v>
+        <v>220.06</v>
       </c>
       <c r="L29" t="n">
         <v>41</v>
@@ -1807,17 +1807,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>4758</v>
       </c>
       <c r="F33" t="n">
-        <v>2192</v>
+        <v>2126</v>
       </c>
       <c r="G33" t="n">
-        <v>53.93</v>
+        <v>55.32</v>
       </c>
       <c r="H33" t="n">
         <v>41.77</v>
@@ -1849,32 +1849,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>15759</v>
       </c>
       <c r="F34" t="n">
-        <v>1840</v>
+        <v>1443</v>
       </c>
       <c r="G34" t="n">
-        <v>88.31999999999999</v>
+        <v>90.84</v>
       </c>
       <c r="H34" t="n">
         <v>42.97</v>
       </c>
       <c r="I34" t="n">
-        <v>47.76</v>
+        <v>46.56</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>252.24</v>
+        <v>253.44</v>
       </c>
       <c r="L34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -1975,32 +1975,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) 1))</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>7758</v>
       </c>
       <c r="F37" t="n">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="G37" t="n">
-        <v>83.2</v>
+        <v>83.23</v>
       </c>
       <c r="H37" t="n">
         <v>41.77</v>
       </c>
       <c r="I37" t="n">
-        <v>46.56</v>
+        <v>44.16</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>253.44</v>
+        <v>255.84</v>
       </c>
       <c r="L37" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (Vec in_1_1 (- in_1_0) (- in_1_1) in_2_1 (- in_2_0) (- in_2_1) in_1_1 (- in_1_0) (- in_1_1))) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_1_1 1 in_1_1 in_2_1 in_2_0 in_2_1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) 9))) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_1_1 1 in_1_1 in_2_1 in_2_0 in_2_1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2))))</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>9757</v>
       </c>
       <c r="F38" t="n">
-        <v>3212</v>
+        <v>1772</v>
       </c>
       <c r="G38" t="n">
-        <v>67.08</v>
+        <v>81.84</v>
       </c>
       <c r="H38" t="n">
         <v>40.57</v>
@@ -2042,7 +2042,7 @@
         <v>224.85</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0)) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0)) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>37757</v>
       </c>
       <c r="F39" t="n">
-        <v>8312</v>
+        <v>8313</v>
       </c>
       <c r="G39" t="n">
-        <v>77.98999999999999</v>
+        <v>77.98</v>
       </c>
       <c r="H39" t="n">
         <v>40.57</v>
       </c>
       <c r="I39" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>259.43</v>
+        <v>258.23</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (VecMinus (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) (&lt;&lt; (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) 4)))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (VecMinus (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) (&lt;&lt; (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) 4)))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (VecMinus (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) (&lt;&lt; (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) 4)))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (VecMinus (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) (&lt;&lt; (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) 4)))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) 1))</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>29021</v>
       </c>
       <c r="F42" t="n">
-        <v>18689</v>
+        <v>18871</v>
       </c>
       <c r="G42" t="n">
-        <v>35.6</v>
+        <v>34.97</v>
       </c>
       <c r="H42" t="n">
         <v>218.27</v>
@@ -2210,7 +2210,7 @@
         <v>79.34</v>
       </c>
       <c r="L42" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
@@ -2227,29 +2227,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (VecMul (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2) (&lt;&lt; (VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2)) 1)))</t>
+          <t>(VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (VecMul (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2) (&lt;&lt; (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2) 1)))</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>8018</v>
       </c>
       <c r="F43" t="n">
-        <v>7431</v>
+        <v>7427</v>
       </c>
       <c r="G43" t="n">
-        <v>7.32</v>
+        <v>7.37</v>
       </c>
       <c r="H43" t="n">
         <v>182.49</v>
       </c>
       <c r="I43" t="n">
-        <v>288.63</v>
+        <v>254.05</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>11.37</v>
+        <v>45.95</v>
       </c>
       <c r="L43" t="n">
         <v>75</v>
@@ -2269,32 +2269,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2))) (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2)))) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2))) (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2)))) 1))</t>
+          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2)) (VecMul (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2)) (VecMul (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>7761</v>
       </c>
       <c r="F44" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G44" t="n">
-        <v>84.06</v>
+        <v>84.09</v>
       </c>
       <c r="H44" t="n">
         <v>141.92</v>
       </c>
       <c r="I44" t="n">
-        <v>181.29</v>
+        <v>146.71</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>118.71</v>
+        <v>153.29</v>
       </c>
       <c r="L44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -2353,14 +2353,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4)) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>36006</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" t="n">
         <v>99.95999999999999</v>
@@ -2369,16 +2369,16 @@
         <v>7.19</v>
       </c>
       <c r="I46" t="n">
-        <v>8.390000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>391.61</v>
+        <v>392.81</v>
       </c>
       <c r="L46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 v2_16 v2_17 v2_18 v2_19 v2_20 v2_21 v2_22 v2_23 v2_24 v2_25 v2_26 v2_27 v2_28 v2_29 v2_30 v2_31) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5) (* v1_8 5) (* v1_9 5) (* v1_10 5) (* v1_11 5) (* v1_12 5) (* v1_13 5) (* v1_14 5) (* v1_15 5) (* v1_16 5) (* v1_17 5) (* v1_18 5) (* v1_19 5) (* v1_20 5) (* v1_21 5) (* v1_22 5) (* v1_23 5) (* v1_24 5) (* v1_25 5) (* v1_26 5) (* v1_27 5) (* v1_28 5) (* v1_29 5) (* v1_30 5) (* v1_31 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 v2_16 v2_17 v2_18 v2_19 v2_20 v2_21 v2_22 v2_23 v2_24 v2_25 v2_26 v2_27 v2_28 v2_29 v2_30 v2_31) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7 v1_8 v1_9 v1_10 v1_11 v1_12 v1_13 v1_14 v1_15 v1_16 v1_17 v1_18 v1_19 v1_20 v1_21 v1_22 v1_23 v1_24 v1_25 v1_26 v1_27 v1_28 v1_29 v1_30 v1_31) (Vec 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>24006</v>
       </c>
       <c r="F48" t="n">
-        <v>8008</v>
+        <v>108</v>
       </c>
       <c r="G48" t="n">
-        <v>66.64</v>
+        <v>99.55</v>
       </c>
       <c r="H48" t="n">
         <v>39.37</v>
@@ -2462,7 +2462,7 @@
         <v>360.63</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -2479,32 +2479,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>4759</v>
       </c>
       <c r="F49" t="n">
-        <v>977</v>
+        <v>576</v>
       </c>
       <c r="G49" t="n">
-        <v>79.47</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H49" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>78.75</v>
+        <v>77.55</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>321.25</v>
+        <v>322.45</v>
       </c>
       <c r="L49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -2521,32 +2521,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>9760</v>
       </c>
       <c r="F50" t="n">
-        <v>1492</v>
+        <v>1091</v>
       </c>
       <c r="G50" t="n">
-        <v>84.70999999999999</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="H50" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>79.94</v>
+        <v>78.75</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>320.06</v>
+        <v>321.25</v>
       </c>
       <c r="L50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
@@ -2563,29 +2563,29 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_19) (Vec v2_3 v2_19 v2_3 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_19) (Vec v2_3 v2_19 v2_3 v2_19)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_20) (Vec v2_4 v2_20 v2_4 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_20) (Vec v2_4 v2_20 v2_4 v2_20)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2))))) (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (Vec v2_12 v2_28 (* 2 (* v1_12 v2_12)) (* 2 (* v1_28 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (Vec v2_12 v2_28 (* 2 (* v1_12 v2_12)) (* 2 (* v1_28 v2_28)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (Vec v2_13 v2_29 (* 2 (* v1_13 v2_13)) (* 2 (* v1_29 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (Vec v2_13 v2_29 (* 2 (* v1_13 v2_13)) (* 2 (* v1_29 v2_29)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (Vec v2_14 v2_30 (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (Vec v2_14 v2_30 (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (Vec v2_15 v2_31 (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (Vec v2_15 v2_31 (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_19) (Vec v2_3 v2_19 v2_3 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_19) (Vec v2_3 v2_19 v2_3 v2_19)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_20) (Vec v2_4 v2_20 v2_4 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_20) (Vec v2_4 v2_20 v2_4 v2_20)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2))))) (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (Vec v2_12 v2_28 (* 2 (* v1_12 v2_12)) (* 2 (* v1_28 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (Vec v2_12 v2_28 (* 2 (* v1_12 v2_12)) (* 2 (* v1_28 v2_28)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (Vec v2_13 v2_29 (* 2 (* v1_13 v2_13)) (* 2 (* v1_29 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (Vec v2_13 v2_29 (* 2 (* v1_13 v2_13)) (* 2 (* v1_29 v2_29)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (Vec v2_14 v2_30 (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (Vec v2_14 v2_30 (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (Vec v2_15 v2_31 (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (Vec v2_15 v2_31 (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) (&lt;&lt; (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) (&lt;&lt; (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) 2))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) (&lt;&lt; (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) (&lt;&lt; (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) 2))))))) 1))</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>39762</v>
       </c>
       <c r="F51" t="n">
-        <v>8181</v>
+        <v>6577</v>
       </c>
       <c r="G51" t="n">
-        <v>79.43000000000001</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="H51" t="n">
         <v>78.75</v>
       </c>
       <c r="I51" t="n">
-        <v>85.93000000000001</v>
+        <v>81.14</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>314.07</v>
+        <v>318.86</v>
       </c>
       <c r="L51" t="n">
         <v>75</v>
@@ -2689,32 +2689,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_0 c2_2) (Vec c1_0 c1_2 c1_0 c1_2)) (&lt;&lt; (VecMinus (Vec c2_0 c2_2 c2_0 c2_2) (Vec c1_0 c1_2 c1_0 c1_2)) 2)) (VecMul (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) (&lt;&lt; (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_0 c2_2) (Vec c1_0 c1_2 c1_0 c1_2)) (&lt;&lt; (VecMinus (Vec c2_0 c2_2 c2_0 c2_2) (Vec c1_0 c1_2 c1_0 c1_2)) 2)) (VecMul (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) (&lt;&lt; (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) 2))) 1))</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>3757</v>
       </c>
       <c r="F54" t="n">
-        <v>3757</v>
+        <v>372</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H54" t="n">
         <v>40.57</v>
       </c>
       <c r="I54" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>359.43</v>
+        <v>357.03</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>7758</v>
       </c>
       <c r="F55" t="n">
-        <v>950</v>
+        <v>752</v>
       </c>
       <c r="G55" t="n">
-        <v>87.75</v>
+        <v>90.31</v>
       </c>
       <c r="H55" t="n">
         <v>41.77</v>
@@ -2773,32 +2773,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24) (Vec c1_8 c1_24 c1_8 c1_24)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24) (Vec c1_8 c1_24 c1_8 c1_24)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25) (Vec c1_9 c1_25 c1_9 c1_25)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25) (Vec c1_9 c1_25 c1_9 c1_25)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26) (Vec c1_10 c1_26 c1_10 c1_26)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26) (Vec c1_10 c1_26 c1_10 c1_26)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27) (Vec c1_11 c1_27 c1_11 c1_27)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27) (Vec c1_11 c1_27 c1_11 c1_27)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28) (Vec c1_12 c1_28 c1_12 c1_28)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28) (Vec c1_12 c1_28 c1_12 c1_28)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24) (Vec c1_8 c1_24 c1_8 c1_24)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24) (Vec c1_8 c1_24 c1_8 c1_24)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25) (Vec c1_9 c1_25 c1_9 c1_25)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25) (Vec c1_9 c1_25 c1_9 c1_25)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26) (Vec c1_10 c1_26 c1_10 c1_26)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26) (Vec c1_10 c1_26 c1_10 c1_26)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27) (Vec c1_11 c1_27 c1_11 c1_27)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27) (Vec c1_11 c1_27 c1_11 c1_27)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28) (Vec c1_12 c1_28 c1_12 c1_28)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28) (Vec c1_12 c1_28 c1_12 c1_28)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>31760</v>
       </c>
       <c r="F56" t="n">
-        <v>3619</v>
+        <v>2824</v>
       </c>
       <c r="G56" t="n">
-        <v>88.61</v>
+        <v>91.11</v>
       </c>
       <c r="H56" t="n">
         <v>44.16</v>
       </c>
       <c r="I56" t="n">
-        <v>51.35</v>
+        <v>47.76</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>348.65</v>
+        <v>352.24</v>
       </c>
       <c r="L56" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57">
@@ -2815,32 +2815,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v2_0 v2_2) (&lt;&lt; (Vec v1_0 v1_2 v2_0 v2_2) 2)) (VecMul (Vec v1_1 v1_3 v2_1 v2_3) (&lt;&lt; (Vec v1_1 v1_3 v2_1 v2_3) 2))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v2_0 v2_2) (&lt;&lt; (Vec v1_0 v1_2 v2_0 v2_2) 2)) (VecMul (Vec v1_1 v1_3 v2_1 v2_3) (&lt;&lt; (Vec v1_1 v1_3 v2_1 v2_3) 2))) 1))</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>1756</v>
       </c>
       <c r="F57" t="n">
-        <v>1756</v>
+        <v>369</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="H57" t="n">
         <v>39.37</v>
       </c>
       <c r="I57" t="n">
-        <v>39.37</v>
+        <v>41.77</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>360.63</v>
+        <v>358.23</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -2899,32 +2899,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))) (+ (+ (+ (+ (* v1_16 v2_16) (* v1_17 v2_17)) (+ (* v1_18 v2_18) (* v1_19 v2_19))) (+ (+ (* v1_20 v2_20) (* v1_21 v2_21)) (+ (* v1_22 v2_22) (* v1_23 v2_23)))) (+ (+ (+ (* v1_24 v2_24) (* v1_25 v2_25)) (+ (* v1_26 v2_26) (* v1_27 v2_27))) (+ (+ (* v1_28 v2_28) (* v1_29 v2_29)) (+ (* v1_30 v2_30) (* v1_31 v2_31)))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>15759</v>
       </c>
       <c r="F59" t="n">
-        <v>15759</v>
+        <v>2542</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>83.87</v>
       </c>
       <c r="H59" t="n">
         <v>42.97</v>
       </c>
       <c r="I59" t="n">
-        <v>42.97</v>
+        <v>45.36</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>357.03</v>
+        <v>354.64</v>
       </c>
       <c r="L59" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60">
@@ -2941,14 +2941,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0)) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecMinus (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) (&lt;&lt; (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) 16))) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecMinus (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) (&lt;&lt; (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) 16)))) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>21507</v>
       </c>
       <c r="F60" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G60" t="n">
         <v>97.61</v>
@@ -2957,16 +2957,16 @@
         <v>40.57</v>
       </c>
       <c r="I60" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>358.23</v>
+        <v>357.03</v>
       </c>
       <c r="L60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
@@ -3109,17 +3109,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) (&lt;&lt; (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) 1))</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (Vec x9604 (+ (* x9613 x9615) x9617))) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (Vec x9604 (+ (* x9613 x9615) x9617))) 1))</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>1508</v>
       </c>
       <c r="F64" t="n">
-        <v>911</v>
+        <v>716</v>
       </c>
       <c r="G64" t="n">
-        <v>39.59</v>
+        <v>52.52</v>
       </c>
       <c r="H64" t="n">
         <v>73.95</v>
@@ -3134,7 +3134,7 @@
         <v>324.85</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>19761</v>
       </c>
       <c r="F72" t="n">
-        <v>19761</v>
+        <v>2120</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>89.27</v>
       </c>
       <c r="H72" t="n">
         <v>77.55</v>
       </c>
       <c r="I72" t="n">
-        <v>77.55</v>
+        <v>79.94</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>322.45</v>
+        <v>320.06</v>
       </c>
       <c r="L72" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73">
@@ -3613,17 +3613,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>4758</v>
       </c>
       <c r="F76" t="n">
-        <v>2192</v>
+        <v>2126</v>
       </c>
       <c r="G76" t="n">
-        <v>53.93</v>
+        <v>55.32</v>
       </c>
       <c r="H76" t="n">
         <v>41.77</v>
@@ -3655,32 +3655,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15) (Vec c1_7 c1_15 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15) (Vec c1_7 c1_15 c1_7 c1_15)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15) (Vec c1_7 c1_15 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15) (Vec c1_7 c1_15 c1_7 c1_15)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>15759</v>
       </c>
       <c r="F77" t="n">
-        <v>15759</v>
+        <v>1377</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="H77" t="n">
         <v>42.97</v>
       </c>
       <c r="I77" t="n">
-        <v>42.97</v>
+        <v>46.56</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>357.03</v>
+        <v>353.44</v>
       </c>
       <c r="L77" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
@@ -3697,32 +3697,32 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( * v1_2 v2_2 ) ) )</t>
+          <t>(VecAdd (VecMul (Vec (+ (* v1_0 v2_0) (* v1_1 v2_1)) v1_2 1 v2_2) (&lt;&lt; (Vec (+ (* v1_0 v2_0) (* v1_1 v2_1)) v1_2 1 v2_2) 2)) (&lt;&lt; (VecMul (Vec (+ (* v1_0 v2_0) (* v1_1 v2_1)) v1_2 1 v2_2) (&lt;&lt; (Vec (+ (* v1_0 v2_0) (* v1_1 v2_1)) v1_2 1 v2_2) 2)) 1))</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>1256</v>
       </c>
       <c r="F78" t="n">
-        <v>1256</v>
+        <v>966</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>23.09</v>
       </c>
       <c r="H78" t="n">
         <v>39.37</v>
       </c>
       <c r="I78" t="n">
-        <v>39.37</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>360.63</v>
+        <v>323.65</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec (* v1_0 v2_0) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) (&lt;&lt; (VecAdd (Vec (* v1_0 v2_0) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) (&lt;&lt; (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) 2)) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) (&lt;&lt; (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) 2)) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) 1))</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>2257</v>
       </c>
       <c r="F79" t="n">
-        <v>1215</v>
+        <v>1122</v>
       </c>
       <c r="G79" t="n">
-        <v>46.17</v>
+        <v>50.29</v>
       </c>
       <c r="H79" t="n">
         <v>40.57</v>
       </c>
       <c r="I79" t="n">
-        <v>41.77</v>
+        <v>77.55</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>358.23</v>
+        <v>322.45</v>
       </c>
       <c r="L79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -3781,32 +3781,32 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecAdd (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2)) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecAdd (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2)) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) 1))</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>7758</v>
       </c>
       <c r="F80" t="n">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G80" t="n">
-        <v>83.22</v>
+        <v>83.23</v>
       </c>
       <c r="H80" t="n">
         <v>41.77</v>
       </c>
       <c r="I80" t="n">
-        <v>45.36</v>
+        <v>44.16</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>354.64</v>
+        <v>355.84</v>
       </c>
       <c r="L80" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -3865,29 +3865,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0)) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0)) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (VecNeg (Vec 0 2 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 0 2 2 2 0)))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>37757</v>
       </c>
       <c r="F82" t="n">
-        <v>8312</v>
+        <v>5314</v>
       </c>
       <c r="G82" t="n">
-        <v>77.98999999999999</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="H82" t="n">
         <v>40.57</v>
       </c>
       <c r="I82" t="n">
-        <v>40.57</v>
+        <v>42.8</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>359.43</v>
+        <v>357.2</v>
       </c>
       <c r="L82" t="n">
         <v>10</v>
@@ -4033,29 +4033,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (* 1 (+ x10162 x10163)) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) (&lt;&lt; (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (* 1 (+ x10162 x10163)) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) 1))</t>
+          <t>(VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (VecMul (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2) (&lt;&lt; (VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2)) 1)))</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>8018</v>
       </c>
       <c r="F86" t="n">
-        <v>8171</v>
+        <v>7431</v>
       </c>
       <c r="G86" t="n">
-        <v>-1.91</v>
+        <v>7.32</v>
       </c>
       <c r="H86" t="n">
         <v>182.49</v>
       </c>
       <c r="I86" t="n">
-        <v>184.88</v>
+        <v>288.63</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>215.12</v>
+        <v>111.37</v>
       </c>
       <c r="L86" t="n">
         <v>75</v>
@@ -4075,32 +4075,32 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2))) (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2)))) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2))) (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2)))) 1))</t>
+          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2)) (VecMul (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2)) (VecMul (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E87" t="n">
         <v>7761</v>
       </c>
       <c r="F87" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G87" t="n">
-        <v>84.06</v>
+        <v>84.09</v>
       </c>
       <c r="H87" t="n">
         <v>141.92</v>
       </c>
       <c r="I87" t="n">
-        <v>181.29</v>
+        <v>146.71</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>218.71</v>
+        <v>253.29</v>
       </c>
       <c r="L87" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
@@ -4159,14 +4159,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4)) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>36006</v>
       </c>
       <c r="F89" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G89" t="n">
         <v>99.95999999999999</v>
@@ -4175,16 +4175,16 @@
         <v>7.19</v>
       </c>
       <c r="I89" t="n">
-        <v>8.390000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>491.61</v>
+        <v>492.81</v>
       </c>
       <c r="L89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -4285,32 +4285,32 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E92" t="n">
         <v>4759</v>
       </c>
       <c r="F92" t="n">
-        <v>977</v>
+        <v>576</v>
       </c>
       <c r="G92" t="n">
-        <v>79.47</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H92" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I92" t="n">
-        <v>78.75</v>
+        <v>77.55</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>421.25</v>
+        <v>422.45</v>
       </c>
       <c r="L92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -4327,32 +4327,32 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>9760</v>
       </c>
       <c r="F93" t="n">
-        <v>1492</v>
+        <v>1091</v>
       </c>
       <c r="G93" t="n">
-        <v>84.70999999999999</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="H93" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>79.94</v>
+        <v>78.75</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>420.06</v>
+        <v>421.25</v>
       </c>
       <c r="L93" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
@@ -4369,29 +4369,29 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_19) (Vec v2_3 v2_19 v2_3 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_19) (Vec v2_3 v2_19 v2_3 v2_19)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_20) (Vec v2_4 v2_20 v2_4 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_20) (Vec v2_4 v2_20 v2_4 v2_20)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2))))) (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (Vec v2_12 v2_28 (* 2 (* v1_12 v2_12)) (* 2 (* v1_28 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (Vec v2_12 v2_28 (* 2 (* v1_12 v2_12)) (* 2 (* v1_28 v2_28)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (Vec v2_13 v2_29 (* 2 (* v1_13 v2_13)) (* 2 (* v1_29 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (Vec v2_13 v2_29 (* 2 (* v1_13 v2_13)) (* 2 (* v1_29 v2_29)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (Vec v2_14 v2_30 (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (Vec v2_14 v2_30 (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (Vec v2_15 v2_31 (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (Vec v2_15 v2_31 (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_19) (Vec v2_3 v2_19 v2_3 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_19) (Vec v2_3 v2_19 v2_3 v2_19)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_20) (Vec v2_4 v2_20 v2_4 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_20) (Vec v2_4 v2_20 v2_4 v2_20)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2))))) (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (Vec v2_12 v2_28 (* 2 (* v1_12 v2_12)) (* 2 (* v1_28 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (Vec v2_12 v2_28 (* 2 (* v1_12 v2_12)) (* 2 (* v1_28 v2_28)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (Vec v2_13 v2_29 (* 2 (* v1_13 v2_13)) (* 2 (* v1_29 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (Vec v2_13 v2_29 (* 2 (* v1_13 v2_13)) (* 2 (* v1_29 v2_29)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (Vec v2_14 v2_30 (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (Vec v2_14 v2_30 (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (Vec v2_15 v2_31 (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (Vec v2_15 v2_31 (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) (&lt;&lt; (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) (&lt;&lt; (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) 2))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) (&lt;&lt; (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) (&lt;&lt; (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) 2))))))) 1))</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>39762</v>
       </c>
       <c r="F94" t="n">
-        <v>8181</v>
+        <v>6577</v>
       </c>
       <c r="G94" t="n">
-        <v>79.43000000000001</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="H94" t="n">
         <v>78.75</v>
       </c>
       <c r="I94" t="n">
-        <v>85.93000000000001</v>
+        <v>81.14</v>
       </c>
       <c r="J94" t="b">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>414.07</v>
+        <v>418.86</v>
       </c>
       <c r="L94" t="n">
         <v>75</v>
@@ -4495,17 +4495,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) (&lt;&lt; (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) (&lt;&lt; (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_3 c2_1 c2_3 c1_1 c1_3 c1_1 c1_3) (&lt;&lt; (Vec c2_1 c2_3 c2_1 c2_3 c1_1 c1_3 c1_1 c1_3) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_3 c2_1 c2_3 c1_1 c1_3 c1_1 c1_3) (&lt;&lt; (Vec c2_1 c2_3 c2_1 c2_3 c1_1 c1_3 c1_1 c1_3) 4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) (&lt;&lt; (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) (&lt;&lt; (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_3 c2_1 c2_3 c1_1 c1_3 c1_1 c1_3) (&lt;&lt; (Vec c2_1 c2_3 c2_1 c2_3 c1_1 c1_3 c1_1 c1_3) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_3 c2_1 c2_3 c1_1 c1_3 c1_1 c1_3) (&lt;&lt; (Vec c2_1 c2_3 c2_1 c2_3 c1_1 c1_3 c1_1 c1_3) 4)) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) (&lt;&lt; (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) (&lt;&lt; (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) (&lt;&lt; (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) (&lt;&lt; (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) (&lt;&lt; (Vec c2_0 c2_2 c2_0 c2_2 c1_0 c1_2 c1_0 c1_2) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) (&lt;&lt; (VecMinus (Vec c2_1 c2_3 c2_1 c2_3) (Vec c1_1 c1_3 c1_1 c1_3)) 2))) 1))</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>3757</v>
       </c>
       <c r="F97" t="n">
-        <v>505</v>
+        <v>439</v>
       </c>
       <c r="G97" t="n">
-        <v>86.56</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="H97" t="n">
         <v>40.57</v>
@@ -4537,17 +4537,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>7758</v>
       </c>
       <c r="F98" t="n">
-        <v>950</v>
+        <v>884</v>
       </c>
       <c r="G98" t="n">
-        <v>87.75</v>
+        <v>88.61</v>
       </c>
       <c r="H98" t="n">
         <v>41.77</v>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E99" t="n">
         <v>31760</v>
       </c>
       <c r="F99" t="n">
-        <v>3619</v>
+        <v>3088</v>
       </c>
       <c r="G99" t="n">
-        <v>88.61</v>
+        <v>90.28</v>
       </c>
       <c r="H99" t="n">
         <v>44.16</v>
       </c>
       <c r="I99" t="n">
-        <v>51.35</v>
+        <v>47.76</v>
       </c>
       <c r="J99" t="b">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>448.65</v>
+        <v>452.24</v>
       </c>
       <c r="L99" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100">
@@ -4705,32 +4705,32 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2))) (VecAdd (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2)) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2))) (VecAdd (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2)) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2))))) (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecAdd (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2)) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2))) (VecAdd (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2)) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2))) (VecAdd (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2)) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2))))) (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecAdd (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2)) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E102" t="n">
         <v>15759</v>
       </c>
       <c r="F102" t="n">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="G102" t="n">
-        <v>83.84999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H102" t="n">
         <v>42.97</v>
       </c>
       <c r="I102" t="n">
-        <v>48.96</v>
+        <v>45.36</v>
       </c>
       <c r="J102" t="b">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>451.04</v>
+        <v>454.64</v>
       </c>
       <c r="L102" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0)) (VecAdd (VecMinus (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0)) (&lt;&lt; (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0)) 16)) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecMinus (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) (&lt;&lt; (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) 16)))) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
         </is>
       </c>
       <c r="E103" t="n">
         <v>21507</v>
       </c>
       <c r="F103" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G103" t="n">
         <v>97.61</v>
@@ -4763,16 +4763,16 @@
         <v>40.57</v>
       </c>
       <c r="I103" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="J103" t="b">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>458.23</v>
+        <v>457.03</v>
       </c>
       <c r="L103" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104">
@@ -4915,32 +4915,32 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) (&lt;&lt; (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) 1))</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) 1))</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>1508</v>
       </c>
       <c r="F107" t="n">
-        <v>911</v>
+        <v>522</v>
       </c>
       <c r="G107" t="n">
-        <v>39.59</v>
+        <v>65.38</v>
       </c>
       <c r="H107" t="n">
         <v>73.95</v>
       </c>
       <c r="I107" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J107" t="b">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>424.85</v>
+        <v>423.65</v>
       </c>
       <c r="L107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -5083,32 +5083,32 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 5 5 5 5) (&lt;&lt; (Vec v1_0 v1_1 v1_2 v1_3 5 5 5 5) 4))))</t>
         </is>
       </c>
       <c r="E111" t="n">
         <v>3006</v>
       </c>
       <c r="F111" t="n">
-        <v>1008</v>
+        <v>163</v>
       </c>
       <c r="G111" t="n">
-        <v>66.47</v>
+        <v>94.58</v>
       </c>
       <c r="H111" t="n">
         <v>39.37</v>
       </c>
       <c r="I111" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="J111" t="b">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>460.63</v>
+        <v>459.43</v>
       </c>
       <c r="L111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -5234,7 +5234,7 @@
         <v>420.06</v>
       </c>
       <c r="L114" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
@@ -5251,29 +5251,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) 2))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E115" t="n">
         <v>19761</v>
       </c>
       <c r="F115" t="n">
-        <v>2522</v>
+        <v>2120</v>
       </c>
       <c r="G115" t="n">
-        <v>87.23999999999999</v>
+        <v>89.27</v>
       </c>
       <c r="H115" t="n">
         <v>77.55</v>
       </c>
       <c r="I115" t="n">
-        <v>82.34</v>
+        <v>79.94</v>
       </c>
       <c r="J115" t="b">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>417.66</v>
+        <v>420.06</v>
       </c>
       <c r="L115" t="n">
         <v>41</v>
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E119" t="n">
         <v>4758</v>
       </c>
       <c r="F119" t="n">
-        <v>4758</v>
+        <v>2126</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>55.32</v>
       </c>
       <c r="H119" t="n">
         <v>41.77</v>
       </c>
       <c r="I119" t="n">
-        <v>41.77</v>
+        <v>79.94</v>
       </c>
       <c r="J119" t="b">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>458.23</v>
+        <v>420.06</v>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15) (Vec c1_7 c1_15 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15) (Vec c1_7 c1_15 c1_7 c1_15)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15) (Vec c1_7 c1_15 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15) (Vec c1_7 c1_15 c1_7 c1_15)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>15759</v>
       </c>
       <c r="F120" t="n">
-        <v>15759</v>
+        <v>1377</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="H120" t="n">
         <v>42.97</v>
       </c>
       <c r="I120" t="n">
-        <v>42.97</v>
+        <v>46.56</v>
       </c>
       <c r="J120" t="b">
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>457.03</v>
+        <v>453.44</v>
       </c>
       <c r="L120" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121">
@@ -5545,32 +5545,32 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec (* v1_0 v2_0) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) (&lt;&lt; (VecAdd (Vec (* v1_0 v2_0) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) (&lt;&lt; (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) 2)) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) (&lt;&lt; (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) 2)) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) 1))</t>
         </is>
       </c>
       <c r="E122" t="n">
         <v>2257</v>
       </c>
       <c r="F122" t="n">
-        <v>1215</v>
+        <v>1122</v>
       </c>
       <c r="G122" t="n">
-        <v>46.17</v>
+        <v>50.29</v>
       </c>
       <c r="H122" t="n">
         <v>40.57</v>
       </c>
       <c r="I122" t="n">
-        <v>41.77</v>
+        <v>77.55</v>
       </c>
       <c r="J122" t="b">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>458.23</v>
+        <v>422.45</v>
       </c>
       <c r="L122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
@@ -5587,32 +5587,32 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) 1))</t>
         </is>
       </c>
       <c r="E123" t="n">
         <v>7758</v>
       </c>
       <c r="F123" t="n">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="G123" t="n">
-        <v>83.2</v>
+        <v>83.23</v>
       </c>
       <c r="H123" t="n">
         <v>41.77</v>
       </c>
       <c r="I123" t="n">
-        <v>46.56</v>
+        <v>44.16</v>
       </c>
       <c r="J123" t="b">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>453.44</v>
+        <v>455.84</v>
       </c>
       <c r="L123" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124">
@@ -5629,17 +5629,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (Vec in_1_1 (- in_1_0) (- in_1_1) in_2_1 (- in_2_0) (- in_2_1) in_1_1 (- in_1_0) (- in_1_1))) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_1_1 1 in_1_1 in_2_1 in_2_0 in_2_1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) 9))) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_1_1 1 in_1_1 in_2_1 in_2_0 in_2_1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2))))</t>
         </is>
       </c>
       <c r="E124" t="n">
         <v>9757</v>
       </c>
       <c r="F124" t="n">
-        <v>3212</v>
+        <v>1772</v>
       </c>
       <c r="G124" t="n">
-        <v>67.08</v>
+        <v>81.84</v>
       </c>
       <c r="H124" t="n">
         <v>40.57</v>
@@ -5654,7 +5654,7 @@
         <v>424.85</v>
       </c>
       <c r="L124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125">
@@ -5671,32 +5671,32 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0)) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0)) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (VecNeg (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (VecNeg (Vec 0 2 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 0 2 2 2 0)))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E125" t="n">
         <v>37757</v>
       </c>
       <c r="F125" t="n">
-        <v>8312</v>
+        <v>315</v>
       </c>
       <c r="G125" t="n">
-        <v>77.98999999999999</v>
+        <v>99.17</v>
       </c>
       <c r="H125" t="n">
         <v>40.57</v>
       </c>
       <c r="I125" t="n">
-        <v>40.57</v>
+        <v>43.82</v>
       </c>
       <c r="J125" t="b">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>459.43</v>
+        <v>456.18</v>
       </c>
       <c r="L125" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
@@ -5839,29 +5839,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (* 1 (+ x10162 x10163)) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) (&lt;&lt; (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (* 1 (+ x10162 x10163)) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) 1))</t>
+          <t>(VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (VecMul (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2) (&lt;&lt; (VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2)) 1)))</t>
         </is>
       </c>
       <c r="E129" t="n">
         <v>8018</v>
       </c>
       <c r="F129" t="n">
-        <v>8171</v>
+        <v>7431</v>
       </c>
       <c r="G129" t="n">
-        <v>-1.91</v>
+        <v>7.32</v>
       </c>
       <c r="H129" t="n">
         <v>182.49</v>
       </c>
       <c r="I129" t="n">
-        <v>184.88</v>
+        <v>288.63</v>
       </c>
       <c r="J129" t="b">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>315.12</v>
+        <v>211.37</v>
       </c>
       <c r="L129" t="n">
         <v>75</v>
@@ -5881,32 +5881,32 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2))) (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2)))) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2))) (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (VecMul (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2)))) 1))</t>
+          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2)) (VecMul (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) (&lt;&lt; (VecMul (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) (&lt;&lt; (Vec x9604 x9634 x9611 x9641 x9607 x9637 x9614 x9644 x9605 x9635 x9612 x9642 x9608 x9638 x9615 x9645) 8)) 4)) 2)) (VecMul (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) (&lt;&lt; (VecMul (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) (&lt;&lt; (VecMul (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) (&lt;&lt; (Vec x9619 x9649 x9626 x9656 x9622 x9652 x9629 x9659 x9620 x9650 x9627 x9657 x9623 x9653 x9630 x9660) 8)) 4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E130" t="n">
         <v>7761</v>
       </c>
       <c r="F130" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G130" t="n">
-        <v>84.06</v>
+        <v>84.09</v>
       </c>
       <c r="H130" t="n">
         <v>141.92</v>
       </c>
       <c r="I130" t="n">
-        <v>181.29</v>
+        <v>146.71</v>
       </c>
       <c r="J130" t="b">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>318.71</v>
+        <v>353.29</v>
       </c>
       <c r="L130" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
@@ -5965,14 +5965,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4)) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
         </is>
       </c>
       <c r="E132" t="n">
         <v>36006</v>
       </c>
       <c r="F132" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G132" t="n">
         <v>99.95999999999999</v>
@@ -5981,16 +5981,16 @@
         <v>7.19</v>
       </c>
       <c r="I132" t="n">
-        <v>8.390000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="J132" t="b">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>991.61</v>
+        <v>992.8099999999999</v>
       </c>
       <c r="L132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133">
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E135" t="n">
         <v>4759</v>
       </c>
       <c r="F135" t="n">
-        <v>977</v>
+        <v>576</v>
       </c>
       <c r="G135" t="n">
-        <v>79.47</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H135" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>78.75</v>
+        <v>77.55</v>
       </c>
       <c r="J135" t="b">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>921.25</v>
+        <v>922.45</v>
       </c>
       <c r="L135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136">
@@ -6133,32 +6133,32 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E136" t="n">
         <v>9760</v>
       </c>
       <c r="F136" t="n">
-        <v>1492</v>
+        <v>1091</v>
       </c>
       <c r="G136" t="n">
-        <v>84.70999999999999</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="H136" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>79.94</v>
+        <v>78.75</v>
       </c>
       <c r="J136" t="b">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>920.0599999999999</v>
+        <v>921.25</v>
       </c>
       <c r="L136" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137">
@@ -6175,29 +6175,29 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (Vec v2_1 v2_17 (* 2 (* v1_1 v2_1)) (* 2 (* v1_17 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (Vec v2_1 v2_17 (* 2 (* v1_1 v2_1)) (* 2 (* v1_17 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (Vec v2_2 v2_18 (* 2 (* v1_2 v2_2)) (* 2 (* v1_18 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (Vec v2_2 v2_18 (* 2 (* v1_2 v2_2)) (* 2 (* v1_18 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2))))) (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (Vec v2_1 v2_17 (* 2 (* v1_1 v2_1)) (* 2 (* v1_17 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (Vec v2_1 v2_17 (* 2 (* v1_1 v2_1)) (* 2 (* v1_17 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (Vec v2_2 v2_18 (* 2 (* v1_2 v2_2)) (* 2 (* v1_18 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (Vec v2_2 v2_18 (* 2 (* v1_2 v2_2)) (* 2 (* v1_18 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2))))) (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) (&lt;&lt; (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) (&lt;&lt; (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) 2))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) (&lt;&lt; (VecMul (Vec 1 1 v1_10 v1_26) (Vec 2 2 v2_10 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) (&lt;&lt; (Vec 2 2 (* v1_15 v2_15) (* v1_31 v2_31)) 2))))))) 1))</t>
         </is>
       </c>
       <c r="E137" t="n">
         <v>39762</v>
       </c>
       <c r="F137" t="n">
-        <v>8181</v>
+        <v>6577</v>
       </c>
       <c r="G137" t="n">
-        <v>79.43000000000001</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="H137" t="n">
         <v>78.75</v>
       </c>
       <c r="I137" t="n">
-        <v>85.93000000000001</v>
+        <v>81.14</v>
       </c>
       <c r="J137" t="b">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>914.0700000000001</v>
+        <v>918.86</v>
       </c>
       <c r="L137" t="n">
         <v>75</v>
@@ -6343,17 +6343,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6) (Vec c1_2 c1_6 c1_2 c1_6)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7) (Vec c1_3 c1_7 c1_3 c1_7)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E141" t="n">
         <v>7758</v>
       </c>
       <c r="F141" t="n">
-        <v>950</v>
+        <v>752</v>
       </c>
       <c r="G141" t="n">
-        <v>87.75</v>
+        <v>90.31</v>
       </c>
       <c r="H141" t="n">
         <v>41.77</v>
@@ -6385,32 +6385,32 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24) (Vec c1_8 c1_24 c1_8 c1_24)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24) (Vec c1_8 c1_24 c1_8 c1_24)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25) (Vec c1_9 c1_25 c1_9 c1_25)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25) (Vec c1_9 c1_25 c1_9 c1_25)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26) (Vec c1_10 c1_26 c1_10 c1_26)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26) (Vec c1_10 c1_26 c1_10 c1_26)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24) (Vec c1_8 c1_24 c1_8 c1_24)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24) (Vec c1_8 c1_24 c1_8 c1_24)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25) (Vec c1_9 c1_25 c1_9 c1_25)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25) (Vec c1_9 c1_25 c1_9 c1_25)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26) (Vec c1_10 c1_26 c1_10 c1_26)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26) (Vec c1_10 c1_26 c1_10 c1_26)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E142" t="n">
         <v>31760</v>
       </c>
       <c r="F142" t="n">
-        <v>3619</v>
+        <v>2956</v>
       </c>
       <c r="G142" t="n">
-        <v>88.61</v>
+        <v>90.69</v>
       </c>
       <c r="H142" t="n">
         <v>44.16</v>
       </c>
       <c r="I142" t="n">
-        <v>51.35</v>
+        <v>47.76</v>
       </c>
       <c r="J142" t="b">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>948.65</v>
+        <v>952.24</v>
       </c>
       <c r="L142" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="143">
@@ -6427,32 +6427,32 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v2_0 v2_2) (&lt;&lt; (Vec v1_0 v1_2 v2_0 v2_2) 2)) (VecMul (Vec v1_1 v1_3 v2_1 v2_3) (&lt;&lt; (Vec v1_1 v1_3 v2_1 v2_3) 2))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v2_0 v2_2) (&lt;&lt; (Vec v1_0 v1_2 v2_0 v2_2) 2)) (VecMul (Vec v1_1 v1_3 v2_1 v2_3) (&lt;&lt; (Vec v1_1 v1_3 v2_1 v2_3) 2))) 1))</t>
         </is>
       </c>
       <c r="E143" t="n">
         <v>1756</v>
       </c>
       <c r="F143" t="n">
-        <v>1756</v>
+        <v>369</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="H143" t="n">
         <v>39.37</v>
       </c>
       <c r="I143" t="n">
-        <v>39.37</v>
+        <v>41.77</v>
       </c>
       <c r="J143" t="b">
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>960.63</v>
+        <v>958.23</v>
       </c>
       <c r="L143" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4 v2_0 v2_4) (&lt;&lt; (Vec v1_0 v1_4 v2_0 v2_4) 2)) (VecMul (Vec v1_1 v1_5 v2_1 v2_5) (&lt;&lt; (Vec v1_1 v1_5 v2_1 v2_5) 2))) (VecAdd (VecMul (Vec v1_2 v1_6 v2_2 v2_6) (&lt;&lt; (Vec v1_2 v1_6 v2_2 v2_6) 2)) (VecMul (Vec v1_3 v1_7 v2_3 v2_7) (&lt;&lt; (Vec v1_3 v1_7 v2_3 v2_7) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4 v2_0 v2_4) (&lt;&lt; (Vec v1_0 v1_4 v2_0 v2_4) 2)) (VecMul (Vec v1_1 v1_5 v2_1 v2_5) (&lt;&lt; (Vec v1_1 v1_5 v2_1 v2_5) 2))) (VecAdd (VecMul (Vec v1_2 v1_6 v2_2 v2_6) (&lt;&lt; (Vec v1_2 v1_6 v2_2 v2_6) 2)) (VecMul (Vec v1_3 v1_7 v2_3 v2_7) (&lt;&lt; (Vec v1_3 v1_7 v2_3 v2_7) 2)))) 1))</t>
         </is>
       </c>
       <c r="E144" t="n">
         <v>3757</v>
       </c>
       <c r="F144" t="n">
-        <v>3757</v>
+        <v>680</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H144" t="n">
         <v>40.57</v>
       </c>
       <c r="I144" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J144" t="b">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>959.4299999999999</v>
+        <v>957.03</v>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145">
@@ -6511,32 +6511,32 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2))) (VecAdd (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2)) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2))) (VecAdd (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2)) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2))))) (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecAdd (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2)) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2))) (VecAdd (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2)) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2))) (VecAdd (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2)) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2))))) (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecAdd (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2)) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E145" t="n">
         <v>15759</v>
       </c>
       <c r="F145" t="n">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="G145" t="n">
-        <v>83.84999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H145" t="n">
         <v>42.97</v>
       </c>
       <c r="I145" t="n">
-        <v>48.96</v>
+        <v>45.36</v>
       </c>
       <c r="J145" t="b">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>951.04</v>
+        <v>954.64</v>
       </c>
       <c r="L145" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146">
@@ -6553,32 +6553,32 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2))) (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0)) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (Vec 0 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 2 2 0)) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecMinus (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) (&lt;&lt; (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) 16)))) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
         </is>
       </c>
       <c r="E146" t="n">
         <v>21507</v>
       </c>
       <c r="F146" t="n">
-        <v>4879</v>
+        <v>514</v>
       </c>
       <c r="G146" t="n">
-        <v>77.31</v>
+        <v>97.61</v>
       </c>
       <c r="H146" t="n">
         <v>40.57</v>
       </c>
       <c r="I146" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="J146" t="b">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>958.23</v>
+        <v>957.03</v>
       </c>
       <c r="L146" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147">
@@ -6637,32 +6637,32 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * o3 ( - 1 c23 ) ) ( * c23 o2 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * o3 ( - 1 c13 ) ) ( * c13 o1 ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec o3 1 1 o3) (VecMinus (Vec 1 0 0 1) (Vec c23 0 0 c13))) (VecMul (Vec c23 1 1 c13) (Vec o2 c12 (- 1 c12) o1))) (&lt;&lt; (VecAdd (VecMul (Vec o3 1 1 o3) (VecMinus (Vec 1 0 0 1) (Vec c23 0 0 c13))) (VecMul (Vec c23 1 1 c13) (Vec o2 c12 (- 1 c12) o1))) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o3 1 1 o3) (VecMinus (Vec 1 0 0 1) (Vec c23 0 0 c13))) (VecMul (Vec c23 1 1 c13) (Vec o2 c12 (- 1 c12) o1))) (&lt;&lt; (VecAdd (VecMul (Vec o3 1 1 o3) (VecMinus (Vec 1 0 0 1) (Vec c23 0 0 c13))) (VecMul (Vec c23 1 1 c13) (Vec o2 c12 (- 1 c12) o1))) 2)) 1))</t>
         </is>
       </c>
       <c r="E148" t="n">
         <v>3009</v>
       </c>
       <c r="F148" t="n">
-        <v>3009</v>
+        <v>669</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>77.77</v>
       </c>
       <c r="H148" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I148" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J148" t="b">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>924.85</v>
+        <v>922.45</v>
       </c>
       <c r="L148" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -6721,32 +6721,32 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) (&lt;&lt; (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) 1))</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) 1))</t>
         </is>
       </c>
       <c r="E150" t="n">
         <v>1508</v>
       </c>
       <c r="F150" t="n">
-        <v>911</v>
+        <v>522</v>
       </c>
       <c r="G150" t="n">
-        <v>39.59</v>
+        <v>65.38</v>
       </c>
       <c r="H150" t="n">
         <v>73.95</v>
       </c>
       <c r="I150" t="n">
-        <v>75.15000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J150" t="b">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>924.85</v>
+        <v>923.65</v>
       </c>
       <c r="L150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -6847,14 +6847,14 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3)) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
         </is>
       </c>
       <c r="E153" t="n">
         <v>21006</v>
       </c>
       <c r="F153" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G153" t="n">
         <v>99.93000000000001</v>
@@ -6863,16 +6863,16 @@
         <v>7.19</v>
       </c>
       <c r="I153" t="n">
-        <v>8.390000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="J153" t="b">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>991.61</v>
+        <v>992.8099999999999</v>
       </c>
       <c r="L153" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -7040,7 +7040,7 @@
         <v>920.0599999999999</v>
       </c>
       <c r="L157" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
@@ -7057,29 +7057,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) 2)) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) 2))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E158" t="n">
         <v>19761</v>
       </c>
       <c r="F158" t="n">
-        <v>2522</v>
+        <v>2120</v>
       </c>
       <c r="G158" t="n">
-        <v>87.23999999999999</v>
+        <v>89.27</v>
       </c>
       <c r="H158" t="n">
         <v>77.55</v>
       </c>
       <c r="I158" t="n">
-        <v>82.34</v>
+        <v>79.94</v>
       </c>
       <c r="J158" t="b">
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>917.66</v>
+        <v>920.0599999999999</v>
       </c>
       <c r="L158" t="n">
         <v>41</v>
@@ -7225,17 +7225,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) (&lt;&lt; (Vec c2_1 c2_4 c2_1 c2_4 c1_1 c1_4 c1_1 c1_4) 4)) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E162" t="n">
         <v>4758</v>
       </c>
       <c r="F162" t="n">
-        <v>2192</v>
+        <v>2126</v>
       </c>
       <c r="G162" t="n">
-        <v>53.93</v>
+        <v>55.32</v>
       </c>
       <c r="H162" t="n">
         <v>41.77</v>
@@ -7267,32 +7267,32 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13) (Vec c1_5 c1_13 c1_5 c1_13)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14) (Vec c1_6 c1_14 c1_6 c1_14)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E163" t="n">
         <v>15759</v>
       </c>
       <c r="F163" t="n">
-        <v>1840</v>
+        <v>1443</v>
       </c>
       <c r="G163" t="n">
-        <v>88.31999999999999</v>
+        <v>90.84</v>
       </c>
       <c r="H163" t="n">
         <v>42.97</v>
       </c>
       <c r="I163" t="n">
-        <v>47.76</v>
+        <v>46.56</v>
       </c>
       <c r="J163" t="b">
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>952.24</v>
+        <v>953.4400000000001</v>
       </c>
       <c r="L163" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="164">
@@ -7309,32 +7309,32 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( * v1_2 v2_2 ) ) )</t>
+          <t>(VecAdd (VecMul (Vec (+ (* v1_0 v2_0) (* v1_1 v2_1)) v1_2 1 v2_2) (&lt;&lt; (Vec (+ (* v1_0 v2_0) (* v1_1 v2_1)) v1_2 1 v2_2) 2)) (&lt;&lt; (VecMul (Vec (+ (* v1_0 v2_0) (* v1_1 v2_1)) v1_2 1 v2_2) (&lt;&lt; (Vec (+ (* v1_0 v2_0) (* v1_1 v2_1)) v1_2 1 v2_2) 2)) 1))</t>
         </is>
       </c>
       <c r="E164" t="n">
         <v>1256</v>
       </c>
       <c r="F164" t="n">
-        <v>1256</v>
+        <v>966</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>23.09</v>
       </c>
       <c r="H164" t="n">
         <v>39.37</v>
       </c>
       <c r="I164" t="n">
-        <v>39.37</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J164" t="b">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>960.63</v>
+        <v>923.65</v>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -7351,32 +7351,32 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec (* v1_0 v2_0) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) (&lt;&lt; (VecAdd (Vec (* v1_0 v2_0) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) (&lt;&lt; (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) 2)) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) (&lt;&lt; (Vec v1_0 (+ (* v1_2 v2_2) (* v1_3 v2_3)) v2_0 1) 2)) (VecMul (Vec v1_1 v1_4 v2_1 v2_4) (&lt;&lt; (Vec v1_1 v1_4 v2_1 v2_4) 2))) 1))</t>
         </is>
       </c>
       <c r="E165" t="n">
         <v>2257</v>
       </c>
       <c r="F165" t="n">
-        <v>1215</v>
+        <v>1122</v>
       </c>
       <c r="G165" t="n">
-        <v>46.17</v>
+        <v>50.29</v>
       </c>
       <c r="H165" t="n">
         <v>40.57</v>
       </c>
       <c r="I165" t="n">
-        <v>41.77</v>
+        <v>77.55</v>
       </c>
       <c r="J165" t="b">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>958.23</v>
+        <v>922.45</v>
       </c>
       <c r="L165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
@@ -7393,32 +7393,32 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecAdd (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2)) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecAdd (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2)) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) 1))</t>
         </is>
       </c>
       <c r="E166" t="n">
         <v>7758</v>
       </c>
       <c r="F166" t="n">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G166" t="n">
-        <v>83.22</v>
+        <v>83.23</v>
       </c>
       <c r="H166" t="n">
         <v>41.77</v>
       </c>
       <c r="I166" t="n">
-        <v>45.36</v>
+        <v>44.16</v>
       </c>
       <c r="J166" t="b">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>954.64</v>
+        <v>955.84</v>
       </c>
       <c r="L166" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167">
@@ -7435,17 +7435,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (Vec in_1_1 (- in_1_0) (- in_1_1) in_2_1 (- in_2_0) (- in_2_1) in_1_1 (- in_1_0) (- in_1_1))) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_1_1 1 in_1_1 in_2_1 in_2_0 in_2_1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) 9))) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_1_1 1 in_1_1 in_2_1 in_2_0 in_2_1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2))))</t>
         </is>
       </c>
       <c r="E167" t="n">
         <v>9757</v>
       </c>
       <c r="F167" t="n">
-        <v>3212</v>
+        <v>1772</v>
       </c>
       <c r="G167" t="n">
-        <v>67.08</v>
+        <v>81.84</v>
       </c>
       <c r="H167" t="n">
         <v>40.57</v>
@@ -7460,7 +7460,7 @@
         <v>924.85</v>
       </c>
       <c r="L167" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -7477,17 +7477,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (VecNeg (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3))) (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0)) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (VecNeg (Vec 0 2 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 0 2 2 2 0)))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E168" t="n">
         <v>37757</v>
       </c>
       <c r="F168" t="n">
-        <v>3314</v>
+        <v>5314</v>
       </c>
       <c r="G168" t="n">
-        <v>91.22</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="H168" t="n">
         <v>40.57</v>
@@ -7502,7 +7502,7 @@
         <v>957.2</v>
       </c>
       <c r="L168" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (VecMinus (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) (&lt;&lt; (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) 4)))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (VecMinus (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) (&lt;&lt; (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) 4)))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (VecMinus (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) (&lt;&lt; (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) 4)))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (VecMinus (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) (&lt;&lt; (VecMinus (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) (&lt;&lt; (Vec c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0) 8)) 4)))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) 1))</t>
         </is>
       </c>
       <c r="E171" t="n">
         <v>29021</v>
       </c>
       <c r="F171" t="n">
-        <v>18689</v>
+        <v>18871</v>
       </c>
       <c r="G171" t="n">
-        <v>35.6</v>
+        <v>34.97</v>
       </c>
       <c r="H171" t="n">
         <v>218.27</v>
@@ -7628,7 +7628,7 @@
         <v>779.34</v>
       </c>
       <c r="L171" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="172">
@@ -7645,29 +7645,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (* 1 (+ x10162 x10163)) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) (&lt;&lt; (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (* 1 (+ x10162 x10163)) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) 1))</t>
+          <t>(VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (VecMul (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2) (&lt;&lt; (VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2)) 1)))</t>
         </is>
       </c>
       <c r="E172" t="n">
         <v>8018</v>
       </c>
       <c r="F172" t="n">
-        <v>8171</v>
+        <v>7431</v>
       </c>
       <c r="G172" t="n">
-        <v>-1.91</v>
+        <v>7.32</v>
       </c>
       <c r="H172" t="n">
         <v>182.49</v>
       </c>
       <c r="I172" t="n">
-        <v>184.88</v>
+        <v>288.63</v>
       </c>
       <c r="J172" t="b">
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>815.12</v>
+        <v>711.37</v>
       </c>
       <c r="L172" t="n">
         <v>75</v>
@@ -7897,32 +7897,32 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_2 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_2 2 (* v1_2 v2_2)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_3 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_3) (Vec v2_1 v2_3 v2_1 v2_3)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_2) (Vec v2_0 2 2 v2_2)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_3) (Vec 2 2 v2_1 v2_3)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E178" t="n">
         <v>4759</v>
       </c>
       <c r="F178" t="n">
-        <v>977</v>
+        <v>576</v>
       </c>
       <c r="G178" t="n">
-        <v>79.47</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H178" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I178" t="n">
-        <v>78.75</v>
+        <v>77.55</v>
       </c>
       <c r="J178" t="b">
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>8999921.25</v>
+        <v>8999922.449999999</v>
       </c>
       <c r="L178" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179">
@@ -7939,32 +7939,32 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_4 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_4 2 (* v1_4 v2_4)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_5 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_5) (Vec v2_1 v2_5 v2_1 v2_5)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_6 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_6) (Vec v2_2 v2_6 v2_2 v2_6)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_7 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_7) (Vec v2_3 v2_7 v2_3 v2_7)))) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_4) (Vec v2_0 2 2 v2_4)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_5) (Vec 2 2 v2_1 v2_5)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_6) (Vec 2 2 v2_2 v2_6)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_7) (Vec 2 2 v2_3 v2_7)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E179" t="n">
         <v>9760</v>
       </c>
       <c r="F179" t="n">
-        <v>1492</v>
+        <v>1091</v>
       </c>
       <c r="G179" t="n">
-        <v>84.70999999999999</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="H179" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>79.94</v>
+        <v>78.75</v>
       </c>
       <c r="J179" t="b">
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>8999920.060000001</v>
+        <v>8999921.25</v>
       </c>
       <c r="L179" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180">
@@ -7981,14 +7981,14 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) 2)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) 2)) (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2)) (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) 2)) (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_16 0 0) (Vec v2_0 v2_16 (* (* v1_0 v2_0) 2) (* 2 (* v1_16 v2_16)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_17 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_17) (Vec v2_1 v2_17 v2_1 v2_17)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_18 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_18) (Vec v2_2 v2_18 v2_2 v2_18)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_19 0 0) (Vec v2_3 v2_19 (* 2 (* v1_3 v2_3)) (* 2 (* v1_19 v2_19)))) 2)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_20 0 0) (Vec v2_4 v2_20 (* 2 (* v1_4 v2_4)) (* 2 (* v1_20 v2_20)))) 2)) (VecMinus (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_21 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_21) (Vec v2_5 v2_21 v2_5 v2_21)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_22 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_22) (Vec v2_6 v2_22 v2_6 v2_22)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_23 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_23) (Vec v2_7 v2_23 v2_7 v2_23)))) 2))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) (&lt;&lt; (VecAdd (Vec v1_8 v1_24 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_8 v1_24) (Vec v2_8 v2_24 v2_8 v2_24)))) 2)) (VecMinus (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) (&lt;&lt; (VecAdd (Vec v1_9 v1_25 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_9 v1_25) (Vec v2_9 v2_25 v2_9 v2_25)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) (&lt;&lt; (VecAdd (Vec v1_10 v1_26 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_10 v1_26) (Vec v2_10 v2_26 v2_10 v2_26)))) 2)) (VecMinus (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) (&lt;&lt; (VecAdd (Vec v1_11 v1_27 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_11 v1_27) (Vec v2_11 v2_27 v2_11 v2_27)))) 2)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) (&lt;&lt; (VecAdd (Vec v1_12 v1_28 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_12 v1_28) (Vec v2_12 v2_28 v2_12 v2_28)))) 2)) (VecMinus (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) (&lt;&lt; (VecAdd (Vec v1_13 v1_29 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_13 v1_29) (Vec v2_13 v2_29 v2_13 v2_29)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) (&lt;&lt; (VecAdd (Vec v1_14 v1_30 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_14 v1_30) (Vec v2_14 v2_30 v2_14 v2_30)))) 2)) (VecMinus (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) (&lt;&lt; (VecAdd (Vec v1_15 v1_31 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_15 v1_31) (Vec v2_15 v2_31 v2_15 v2_31)))) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2 (* v1_10 v2_10) (* v1_26 v2_26)) (&lt;&lt; (Vec 2 2 (* v1_10 v2_10) (* v1_26 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (VecMul (Vec 1 1 v1_15 v1_31) (Vec 2 2 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec 1 1 v1_15 v1_31) (Vec 2 2 v2_15 v2_31)) 2))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) (&lt;&lt; (Vec (* v1_0 v2_0) 2 2 (* v1_16 v2_16)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_17) (Vec 2 2 v2_1 v2_17)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_18) (Vec 2 2 v2_2 v2_18)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_19) (Vec 2 2 v2_3 v2_19)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_20) (Vec 2 2 v2_4 v2_20)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_21) (Vec 2 2 v2_5 v2_21)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_22) (Vec 2 2 v2_6 v2_22)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_23) (Vec 2 2 v2_7 v2_23)) 2)))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) (&lt;&lt; (VecMul (Vec 1 1 v1_8 v1_24) (Vec 2 2 v2_8 v2_24)) 2))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) (&lt;&lt; (VecMul (Vec 1 1 v1_9 v1_25) (Vec 2 2 v2_9 v2_25)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2 (* v1_10 v2_10) (* v1_26 v2_26)) (&lt;&lt; (Vec 2 2 (* v1_10 v2_10) (* v1_26 v2_26)) 2))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) (&lt;&lt; (Vec 2 2 (* v1_11 v2_11) (* v1_27 v2_27)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) (&lt;&lt; (Vec 2 2 (* v1_12 v2_12) (* v1_28 v2_28)) 2))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) (&lt;&lt; (Vec 2 2 (* v1_13 v2_13) (* v1_29 v2_29)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) (&lt;&lt; (Vec 2 2 (* v1_14 v2_14) (* v1_30 v2_30)) 2))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (VecMul (VecMul (Vec 1 1 v1_15 v1_31) (Vec 2 2 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec 1 1 v1_15 v1_31) (Vec 2 2 v2_15 v2_31)) 2))))))) 1))</t>
         </is>
       </c>
       <c r="E180" t="n">
         <v>39762</v>
       </c>
       <c r="F180" t="n">
-        <v>6578</v>
+        <v>6577</v>
       </c>
       <c r="G180" t="n">
         <v>83.45999999999999</v>
@@ -7997,13 +7997,13 @@
         <v>78.75</v>
       </c>
       <c r="I180" t="n">
-        <v>82.34</v>
+        <v>81.14</v>
       </c>
       <c r="J180" t="b">
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>8999917.66</v>
+        <v>8999918.859999999</v>
       </c>
       <c r="L180" t="n">
         <v>75</v>
@@ -8149,17 +8149,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) (&lt;&lt; (Vec c2_1 c2_5 c2_1 c2_5 c1_1 c1_5 c1_1 c1_5) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) (&lt;&lt; (Vec c2_0 c2_4 c2_0 c2_4 c1_0 c1_4 c1_0 c1_4) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) (&lt;&lt; (VecMinus (Vec c2_1 c2_5 c2_1 c2_5) (Vec c1_1 c1_5 c1_1 c1_5)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) (&lt;&lt; (Vec c2_2 c2_6 c2_2 c2_6 c1_2 c1_6 c1_2 c1_6) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) (&lt;&lt; (Vec c2_3 c2_7 c2_3 c2_7 c1_3 c1_7 c1_3 c1_7) 4)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E184" t="n">
         <v>7758</v>
       </c>
       <c r="F184" t="n">
-        <v>950</v>
+        <v>884</v>
       </c>
       <c r="G184" t="n">
-        <v>87.75</v>
+        <v>88.61</v>
       </c>
       <c r="H184" t="n">
         <v>41.77</v>
@@ -8191,32 +8191,32 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) (&lt;&lt; (Vec c2_1 c2_17 c2_1 c2_17 c1_1 c1_17 c1_1 c1_17) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) (&lt;&lt; (Vec c2_2 c2_18 c2_2 c2_18 c1_2 c1_18 c1_2 c1_18) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) (&lt;&lt; (Vec c2_3 c2_19 c2_3 c2_19 c1_3 c1_19 c1_3 c1_19) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) (&lt;&lt; (Vec c2_4 c2_20 c2_4 c2_20 c1_4 c1_20 c1_4 c1_20) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) (&lt;&lt; (Vec c2_5 c2_21 c2_5 c2_21 c1_5 c1_21 c1_5 c1_21) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) (&lt;&lt; (Vec c2_6 c2_22 c2_6 c2_22 c1_6 c1_22 c1_6 c1_22) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) (&lt;&lt; (Vec c2_7 c2_23 c2_7 c2_23 c1_7 c1_23 c1_7 c1_23) 4)) 2))))) (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2))))) (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) (&lt;&lt; (Vec c2_15 c2_31 c2_15 c2_31 c1_15 c1_31 c1_15 c1_31) 4)) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) (&lt;&lt; (Vec c2_0 c2_16 c2_0 c2_16 c1_0 c1_16 c1_0 c1_16) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) (&lt;&lt; (VecMinus (Vec c2_1 c2_17 c2_1 c2_17) (Vec c1_1 c1_17 c1_1 c1_17)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) (&lt;&lt; (VecMinus (Vec c2_2 c2_18 c2_2 c2_18) (Vec c1_2 c1_18 c1_2 c1_18)) 2)) (VecMul (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) (&lt;&lt; (VecMinus (Vec c2_3 c2_19 c2_3 c2_19) (Vec c1_3 c1_19 c1_3 c1_19)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) (&lt;&lt; (VecMinus (Vec c2_4 c2_20 c2_4 c2_20) (Vec c1_4 c1_20 c1_4 c1_20)) 2)) (VecMul (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) (&lt;&lt; (VecMinus (Vec c2_5 c2_21 c2_5 c2_21) (Vec c1_5 c1_21 c1_5 c1_21)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) (&lt;&lt; (VecMinus (Vec c2_6 c2_22 c2_6 c2_22) (Vec c1_6 c1_22 c1_6 c1_22)) 2)) (VecMul (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) (&lt;&lt; (VecMinus (Vec c2_7 c2_23 c2_7 c2_23) (Vec c1_7 c1_23 c1_7 c1_23)) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) (&lt;&lt; (VecMinus (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) (&lt;&lt; (Vec c2_8 c2_24 c2_8 c2_24 c1_8 c1_24 c1_8 c1_24) 4)) 2)) (VecMul (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) (&lt;&lt; (VecMinus (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) (&lt;&lt; (Vec c2_9 c2_25 c2_9 c2_25 c1_9 c1_25 c1_9 c1_25) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) (&lt;&lt; (VecMinus (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) (&lt;&lt; (Vec c2_10 c2_26 c2_10 c2_26 c1_10 c1_26 c1_10 c1_26) 4)) 2)) (VecMul (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) (&lt;&lt; (VecMinus (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) (&lt;&lt; (Vec c2_11 c2_27 c2_11 c2_27 c1_11 c1_27 c1_11 c1_27) 4)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) (&lt;&lt; (VecMinus (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) (&lt;&lt; (Vec c2_12 c2_28 c2_12 c2_28 c1_12 c1_28 c1_12 c1_28) 4)) 2)) (VecMul (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) (&lt;&lt; (VecMinus (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) (&lt;&lt; (Vec c2_13 c2_29 c2_13 c2_29 c1_13 c1_29 c1_13 c1_29) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) (&lt;&lt; (VecMinus (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) (&lt;&lt; (Vec c2_14 c2_30 c2_14 c2_30 c1_14 c1_30 c1_14 c1_30) 4)) 2)) (VecMul (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) (&lt;&lt; (VecMinus (Vec c2_15 c2_31 c2_15 c2_31) (Vec c1_15 c1_31 c1_15 c1_31)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E185" t="n">
         <v>31760</v>
       </c>
       <c r="F185" t="n">
-        <v>3619</v>
+        <v>3088</v>
       </c>
       <c r="G185" t="n">
-        <v>88.61</v>
+        <v>90.28</v>
       </c>
       <c r="H185" t="n">
         <v>44.16</v>
       </c>
       <c r="I185" t="n">
-        <v>51.35</v>
+        <v>47.76</v>
       </c>
       <c r="J185" t="b">
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>8999948.65</v>
+        <v>8999952.24</v>
       </c>
       <c r="L185" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="186">
@@ -8317,32 +8317,32 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2))) (VecAdd (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2)) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2))) (VecAdd (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2)) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2))))) (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecAdd (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2)) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2))) (VecAdd (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2)) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2))) (VecAdd (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2)) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2))))) (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecAdd (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2)) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v2_0 v2_16) (&lt;&lt; (Vec v1_0 v1_16 v2_0 v2_16) 2)) (VecMul (Vec v1_1 v1_17 v2_1 v2_17) (&lt;&lt; (Vec v1_1 v1_17 v2_1 v2_17) 2))) (VecAdd (VecMul (Vec v1_2 v1_18 v2_2 v2_18) (&lt;&lt; (Vec v1_2 v1_18 v2_2 v2_18) 2)) (VecMul (Vec v1_3 v1_19 v2_3 v2_19) (&lt;&lt; (Vec v1_3 v1_19 v2_3 v2_19) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20 v2_4 v2_20) (&lt;&lt; (Vec v1_4 v1_20 v2_4 v2_20) 2)) (VecMul (Vec v1_5 v1_21 v2_5 v2_21) (&lt;&lt; (Vec v1_5 v1_21 v2_5 v2_21) 2))) (VecAdd (VecMul (Vec v1_6 v1_22 v2_6 v2_22) (&lt;&lt; (Vec v1_6 v1_22 v2_6 v2_22) 2)) (VecMul (Vec v1_7 v1_23 v2_7 v2_23) (&lt;&lt; (Vec v1_7 v1_23 v2_7 v2_23) 2))))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24 v2_8 v2_24) (&lt;&lt; (Vec v1_8 v1_24 v2_8 v2_24) 2)) (VecMul (Vec v1_9 v1_25 v2_9 v2_25) (&lt;&lt; (Vec v1_9 v1_25 v2_9 v2_25) 2))) (VecAdd (VecMul (Vec v1_10 v1_26 v2_10 v2_26) (&lt;&lt; (Vec v1_10 v1_26 v2_10 v2_26) 2)) (VecMul (Vec v1_11 v1_27 v2_11 v2_27) (&lt;&lt; (Vec v1_11 v1_27 v2_11 v2_27) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28 v2_12 v2_28) (&lt;&lt; (Vec v1_12 v1_28 v2_12 v2_28) 2)) (VecMul (Vec v1_13 v1_29 v2_13 v2_29) (&lt;&lt; (Vec v1_13 v1_29 v2_13 v2_29) 2))) (VecAdd (VecMul (Vec v1_14 v1_30 v2_14 v2_30) (&lt;&lt; (Vec v1_14 v1_30 v2_14 v2_30) 2)) (VecMul (Vec v1_15 v1_31 v2_15 v2_31) (&lt;&lt; (Vec v1_15 v1_31 v2_15 v2_31) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E188" t="n">
         <v>15759</v>
       </c>
       <c r="F188" t="n">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="G188" t="n">
-        <v>83.84999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H188" t="n">
         <v>42.97</v>
       </c>
       <c r="I188" t="n">
-        <v>48.96</v>
+        <v>45.36</v>
       </c>
       <c r="J188" t="b">
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>8999951.039999999</v>
+        <v>8999954.640000001</v>
       </c>
       <c r="L188" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="189">
@@ -8359,14 +8359,14 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0)) (VecAdd (VecMinus (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0)) (&lt;&lt; (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0)) 16)) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecMinus (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) (&lt;&lt; (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) 16)))) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) (&lt;&lt; (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2) 16)))))</t>
         </is>
       </c>
       <c r="E189" t="n">
         <v>21507</v>
       </c>
       <c r="F189" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G189" t="n">
         <v>97.61</v>
@@ -8375,16 +8375,16 @@
         <v>40.57</v>
       </c>
       <c r="I189" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="J189" t="b">
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>8999958.23</v>
+        <v>8999957.029999999</v>
       </c>
       <c r="L189" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190">
@@ -8527,17 +8527,17 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) (&lt;&lt; (VecAdd (Vec x9602 (+ x9608 x9610)) (Vec x9604 (+ (* x9613 x9615) x9617))) 1))</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (Vec x9604 (+ (* x9613 x9615) x9617))) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (Vec x9604 (+ (* x9613 x9615) x9617))) 1))</t>
         </is>
       </c>
       <c r="E193" t="n">
         <v>1508</v>
       </c>
       <c r="F193" t="n">
-        <v>911</v>
+        <v>716</v>
       </c>
       <c r="G193" t="n">
-        <v>39.59</v>
+        <v>52.52</v>
       </c>
       <c r="H193" t="n">
         <v>73.95</v>
@@ -8552,7 +8552,7 @@
         <v>8999924.85</v>
       </c>
       <c r="L193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
@@ -8653,14 +8653,14 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3)) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
         </is>
       </c>
       <c r="E196" t="n">
         <v>21006</v>
       </c>
       <c r="F196" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G196" t="n">
         <v>99.93000000000001</v>
@@ -8669,16 +8669,16 @@
         <v>7.19</v>
       </c>
       <c r="I196" t="n">
-        <v>8.390000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="J196" t="b">
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>8999991.609999999</v>
+        <v>8999992.810000001</v>
       </c>
       <c r="L196" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197">
@@ -8695,32 +8695,32 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 5 5 5 5) (&lt;&lt; (Vec v1_0 v1_1 v1_2 v1_3 5 5 5 5) 4))))</t>
         </is>
       </c>
       <c r="E197" t="n">
         <v>3006</v>
       </c>
       <c r="F197" t="n">
-        <v>1008</v>
+        <v>163</v>
       </c>
       <c r="G197" t="n">
-        <v>66.47</v>
+        <v>94.58</v>
       </c>
       <c r="H197" t="n">
         <v>39.37</v>
       </c>
       <c r="I197" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="J197" t="b">
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>8999960.630000001</v>
+        <v>8999959.43</v>
       </c>
       <c r="L197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_4 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_4) (Vec v2_1 v2_4 v2_1 v2_4)))) 2))) 1))</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) (&lt;&lt; (VecAdd (Vec v1_0 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0 0) (Vec v2_0 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))) (* (* v1_0 v2_0) 2) 0)) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_4) (Vec 2 2 v2_1 v2_4)) 2)))) 1))</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -8863,32 +8863,32 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) (&lt;&lt; (VecAdd (Vec v1_0 v1_8 0 0) (VecMul (Vec 1 1 (* v1_0 v2_0) 2) (Vec v2_0 v2_8 2 (* v1_8 v2_8)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) (&lt;&lt; (VecAdd (Vec v1_1 v1_9 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_1 v1_9) (Vec v2_1 v2_9 v2_1 v2_9)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) (&lt;&lt; (VecAdd (Vec v1_2 v1_10 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_2 v1_10) (Vec v2_2 v2_10 v2_2 v2_10)))) 2)) (VecMinus (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) (&lt;&lt; (VecAdd (Vec v1_3 v1_11 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_3 v1_11) (Vec v2_3 v2_11 v2_3 v2_11)))) 2)))) (VecMinus (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) (&lt;&lt; (VecAdd (Vec v1_4 v1_12 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_4 v1_12) (Vec v2_4 v2_12 v2_4 v2_12)))) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) (&lt;&lt; (VecAdd (Vec v1_5 v1_13 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_5 v1_13) (Vec v2_5 v2_13 v2_5 v2_13)))) 2))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) (&lt;&lt; (VecAdd (Vec v1_6 v1_14 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_6 v1_14) (Vec v2_6 v2_14 v2_6 v2_14)))) 2)) (VecMinus (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) (&lt;&lt; (VecAdd (Vec v1_7 v1_15 0 0) (VecMul (Vec 1 1 2 2) (VecMul (Vec 1 1 v1_7 v1_15) (Vec v2_7 v2_15 v2_7 v2_15)))) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) (&lt;&lt; (VecMul (Vec v1_0 1 1 v1_8) (Vec v2_0 2 2 v2_8)) 2))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) (&lt;&lt; (VecMul (Vec 1 1 v1_1 v1_9) (Vec 2 2 v2_1 v2_9)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) (&lt;&lt; (VecMul (Vec 1 1 v1_2 v1_10) (Vec 2 2 v2_2 v2_10)) 2))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) (&lt;&lt; (VecMul (Vec 1 1 v1_3 v1_11) (Vec 2 2 v2_3 v2_11)) 2))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) (&lt;&lt; (VecMul (Vec 1 1 v1_4 v1_12) (Vec 2 2 v2_4 v2_12)) 2))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) (&lt;&lt; (VecMul (Vec 1 1 v1_5 v1_13) (Vec 2 2 v2_5 v2_13)) 2)))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) (&lt;&lt; (VecMul (Vec 1 1 v1_6 v1_14) (Vec 2 2 v2_6 v2_14)) 2))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec 1 1 v1_7 v1_15) (Vec 2 2 v2_7 v2_15)) 2)))))) 1))</t>
         </is>
       </c>
       <c r="E201" t="n">
         <v>19761</v>
       </c>
       <c r="F201" t="n">
-        <v>2523</v>
+        <v>2120</v>
       </c>
       <c r="G201" t="n">
-        <v>87.23</v>
+        <v>89.27</v>
       </c>
       <c r="H201" t="n">
         <v>77.55</v>
       </c>
       <c r="I201" t="n">
-        <v>83.54000000000001</v>
+        <v>79.94</v>
       </c>
       <c r="J201" t="b">
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>8999916.460000001</v>
+        <v>8999920.060000001</v>
       </c>
       <c r="L201" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="202">
@@ -9031,32 +9031,32 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) (&lt;&lt; (VecMinus (Vec c2_0 (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) c2_0 1) (Vec c1_0 0 c1_0 0)) 2)) (VecMul (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_4 c2_1 c2_4) (Vec c1_1 c1_4 c1_1 c1_4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E205" t="n">
         <v>4758</v>
       </c>
       <c r="F205" t="n">
-        <v>4758</v>
+        <v>2126</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>55.32</v>
       </c>
       <c r="H205" t="n">
         <v>41.77</v>
       </c>
       <c r="I205" t="n">
-        <v>41.77</v>
+        <v>79.94</v>
       </c>
       <c r="J205" t="b">
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>8999958.23</v>
+        <v>8999920.060000001</v>
       </c>
       <c r="L205" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206">
@@ -9073,32 +9073,32 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) (&lt;&lt; (Vec c2_1 c2_9 c2_1 c2_9 c1_1 c1_9 c1_1 c1_9) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) (&lt;&lt; (Vec c2_2 c2_10 c2_2 c2_10 c1_2 c1_10 c1_2 c1_10) 4)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) (&lt;&lt; (Vec c2_3 c2_11 c2_3 c2_11 c1_3 c1_11 c1_3 c1_11) 4)) 2)))) (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) (&lt;&lt; (Vec c2_4 c2_12 c2_4 c2_12 c1_4 c1_12 c1_4 c1_12) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) 2)) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) (&lt;&lt; (Vec c2_0 c2_8 c2_0 c2_8 c1_0 c1_8 c1_0 c1_8) 4)) 2)) (VecMul (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) (&lt;&lt; (VecMinus (Vec c2_1 c2_9 c2_1 c2_9) (Vec c1_1 c1_9 c1_1 c1_9)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) (&lt;&lt; (VecMinus (Vec c2_2 c2_10 c2_2 c2_10) (Vec c1_2 c1_10 c1_2 c1_10)) 2)) (VecMul (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) (&lt;&lt; (VecMinus (Vec c2_3 c2_11 c2_3 c2_11) (Vec c1_3 c1_11 c1_3 c1_11)) 2)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) (&lt;&lt; (VecMinus (Vec c2_4 c2_12 c2_4 c2_12) (Vec c1_4 c1_12 c1_4 c1_12)) 2)) (VecMul (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) (&lt;&lt; (VecMinus (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) (&lt;&lt; (Vec c2_5 c2_13 c2_5 c2_13 c1_5 c1_13 c1_5 c1_13) 4)) 2))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) (&lt;&lt; (VecMinus (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) (&lt;&lt; (Vec c2_6 c2_14 c2_6 c2_14 c1_6 c1_14 c1_6 c1_14) 4)) 2)) (VecMul (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) (&lt;&lt; (VecMinus (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) (&lt;&lt; (Vec c2_7 c2_15 c2_7 c2_15 c1_7 c1_15 c1_7 c1_15) 4)) 2))))) 1))</t>
         </is>
       </c>
       <c r="E206" t="n">
         <v>15759</v>
       </c>
       <c r="F206" t="n">
-        <v>1840</v>
+        <v>1575</v>
       </c>
       <c r="G206" t="n">
-        <v>88.31999999999999</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="H206" t="n">
         <v>42.97</v>
       </c>
       <c r="I206" t="n">
-        <v>47.76</v>
+        <v>46.56</v>
       </c>
       <c r="J206" t="b">
         <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>8999952.24</v>
+        <v>8999953.439999999</v>
       </c>
       <c r="L206" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="207">
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2)))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2))) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2)))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8 v2_0 v2_8) (&lt;&lt; (Vec v1_0 v1_8 v2_0 v2_8) 2)) (VecMul (Vec v1_1 v1_9 v2_1 v2_9) (&lt;&lt; (Vec v1_1 v1_9 v2_1 v2_9) 2))) (VecAdd (VecMul (Vec v1_2 v1_10 v2_2 v2_10) (&lt;&lt; (Vec v1_2 v1_10 v2_2 v2_10) 2)) (VecMul (Vec v1_3 v1_11 v2_3 v2_11) (&lt;&lt; (Vec v1_3 v1_11 v2_3 v2_11) 2)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12 v2_4 v2_12) (&lt;&lt; (Vec v1_4 v1_12 v2_4 v2_12) 2)) (VecMul (Vec v1_5 v1_13 v2_5 v2_13) (&lt;&lt; (Vec v1_5 v1_13 v2_5 v2_13) 2))) (VecAdd (VecMul (Vec v1_6 v1_14 v2_6 v2_14) (&lt;&lt; (Vec v1_6 v1_14 v2_6 v2_14) 2)) (VecMul (Vec v1_7 v1_15 v2_7 v2_15) (&lt;&lt; (Vec v1_7 v1_15 v2_7 v2_15) 2))))) 1))</t>
         </is>
       </c>
       <c r="E209" t="n">
         <v>7758</v>
       </c>
       <c r="F209" t="n">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="G209" t="n">
-        <v>83.2</v>
+        <v>83.23</v>
       </c>
       <c r="H209" t="n">
         <v>41.77</v>
       </c>
       <c r="I209" t="n">
-        <v>46.56</v>
+        <v>44.16</v>
       </c>
       <c r="J209" t="b">
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>8999953.439999999</v>
+        <v>8999955.84</v>
       </c>
       <c r="L209" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="210">
@@ -9283,32 +9283,32 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0)) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0)) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>37757</v>
       </c>
       <c r="F211" t="n">
-        <v>8312</v>
+        <v>8313</v>
       </c>
       <c r="G211" t="n">
-        <v>77.98999999999999</v>
+        <v>77.98</v>
       </c>
       <c r="H211" t="n">
         <v>40.57</v>
       </c>
       <c r="I211" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="J211" t="b">
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>8999959.43</v>
+        <v>8999958.23</v>
       </c>
       <c r="L211" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212">
@@ -9409,29 +9409,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 c13)) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* c13 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1))) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* c13 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1))) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* c13 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1))) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 1 (- 1 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* c13 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1))) (Vec (- 1 c23) 0 0 (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))) (VecMul (Vec c23 1 1 c13) (VecAdd (VecMul (Vec (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 1 1 (- 1 c23)) (Vec (- 1 c13) 0 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec c13 1 1 c23) (VecAdd (VecMul (Vec o2134 1 1 o1234) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (VecAdd (VecMul (VecMinus (Vec 1 1 1 1) (Vec c14 0 0 c24)) (VecAdd (VecMul (Vec o4213 1 1 o4123) (VecMinus (Vec 1 0 0 1) (Vec c24 0 0 c14))) (VecMul (Vec c24 1 1 c14) (Vec o2413 0 0 o1423)))) (VecMul (Vec c14 1 1 c24) (VecAdd (VecMul (Vec o2143 1 1 o1243) (VecMinus (Vec 1 0 0 1) (Vec c34 0 0 c34))) (VecMul (Vec c34 1 1 c34) (Vec o2134 c12 (- 1 c12) o1234))))))))))) 2)) 1))</t>
         </is>
       </c>
       <c r="E214" t="n">
         <v>29021</v>
       </c>
       <c r="F214" t="n">
-        <v>18689</v>
+        <v>31277</v>
       </c>
       <c r="G214" t="n">
-        <v>35.6</v>
+        <v>-7.77</v>
       </c>
       <c r="H214" t="n">
         <v>218.27</v>
       </c>
       <c r="I214" t="n">
-        <v>220.66</v>
+        <v>1806.6</v>
       </c>
       <c r="J214" t="b">
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>8999779.34</v>
+        <v>8998193.4</v>
       </c>
       <c r="L214" t="n">
         <v>75</v>
@@ -9451,29 +9451,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (* 1 (+ x10162 x10163)) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) (&lt;&lt; (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (* 1 (+ x10162 x10163)) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) 1))</t>
+          <t>(VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (VecMul (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2) (&lt;&lt; (VecMul (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) (&lt;&lt; (VecMul (Vec (+ (* (* x10106 x10108) x10110) x10112) 1 x10117 1) (Vec x10115 (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183)) x10119 1)) 2)) 1)))</t>
         </is>
       </c>
       <c r="E215" t="n">
         <v>8018</v>
       </c>
       <c r="F215" t="n">
-        <v>8171</v>
+        <v>7431</v>
       </c>
       <c r="G215" t="n">
-        <v>-1.91</v>
+        <v>7.32</v>
       </c>
       <c r="H215" t="n">
         <v>182.49</v>
       </c>
       <c r="I215" t="n">
-        <v>184.88</v>
+        <v>288.63</v>
       </c>
       <c r="J215" t="b">
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>8999815.119999999</v>
+        <v>8999711.369999999</v>
       </c>
       <c r="L215" t="n">
         <v>75</v>
@@ -9585,10 +9585,10 @@
         <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>70.86</v>
+        <v>77.28</v>
       </c>
       <c r="D2" t="n">
-        <v>75.66</v>
+        <v>73.72</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9597,10 +9597,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>224.34</v>
+        <v>226.28</v>
       </c>
       <c r="H2" t="n">
-        <v>15.7</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="3">
@@ -9611,10 +9611,10 @@
         <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>64.79000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>71.17</v>
+        <v>74.55</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -9623,10 +9623,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>328.83</v>
+        <v>325.45</v>
       </c>
       <c r="H3" t="n">
-        <v>18.5</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="4">
@@ -9637,10 +9637,10 @@
         <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>71.67</v>
+        <v>78.02</v>
       </c>
       <c r="D4" t="n">
-        <v>71.53</v>
+        <v>74.63</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -9649,10 +9649,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>428.47</v>
+        <v>425.37</v>
       </c>
       <c r="H4" t="n">
-        <v>18.5</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="5">
@@ -9663,10 +9663,10 @@
         <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>69.39</v>
+        <v>77.69</v>
       </c>
       <c r="D5" t="n">
-        <v>70.78</v>
+        <v>74.61</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -9675,10 +9675,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>929.22</v>
+        <v>925.39</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="6">
@@ -9689,10 +9689,10 @@
         <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>74.26000000000001</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>71.62</v>
+        <v>111.44</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -9701,10 +9701,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>8999928.380000001</v>
+        <v>8999888.560000001</v>
       </c>
       <c r="H6" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
     </row>
   </sheetData>
